--- a/src/attributions/attributions_ig_traj_127.xlsx
+++ b/src/attributions/attributions_ig_traj_127.xlsx
@@ -1571,7 +1571,7 @@
         <v>-0</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.5027264699901006</v>
+        <v>-0.3588770592658792</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -1580,25 +1580,25 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01828436989046878</v>
+        <v>-0.05532372866082529</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6676571977912784</v>
+        <v>0.2210510390413825</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1040086735901935</v>
+        <v>-0.1084542491768875</v>
       </c>
       <c r="L3" t="n">
         <v>-0</v>
@@ -1607,37 +1607,37 @@
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.09161148816893128</v>
+        <v>0.02239741568216909</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2438255726818518</v>
+        <v>0.1078732416245839</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003339681265428182</v>
+        <v>-0.1597800396366528</v>
       </c>
       <c r="U3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2521553727442762</v>
+        <v>0.1055966520206997</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.01101138711278343</v>
+        <v>0.08741214857611511</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1646,25 +1646,25 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.1748403233431227</v>
+        <v>0.1239491406903126</v>
       </c>
       <c r="AD3" t="n">
         <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.1058106464584909</v>
+        <v>0.1563099717383144</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.02384449154574922</v>
+        <v>0.03090238732789875</v>
       </c>
       <c r="AH3" t="n">
         <v>-0</v>
@@ -1676,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.02966691018374555</v>
+        <v>-0.1264853838791857</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1688,25 +1688,25 @@
         <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.04108088690785633</v>
+        <v>-0.1307976105517814</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1914674750330189</v>
+        <v>0.07359740971269887</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.5235037745053465</v>
+        <v>-0.50357025498201</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1715,25 +1715,25 @@
         <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1496489113039587</v>
+        <v>0.03503211236482996</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.5488419529259585</v>
+        <v>0.1448181466356344</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
         <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.0402196912504493</v>
+        <v>0.007860814285078678</v>
       </c>
       <c r="BE3" t="n">
         <v>-0</v>
@@ -1742,106 +1742,106 @@
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.06039441407892389</v>
+        <v>0.008417357618890425</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1294017726708695</v>
+        <v>0.04972995020388118</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL3" t="n">
         <v>-0</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.05130578619478099</v>
+        <v>0.1083501100665745</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.03559945456508799</v>
+        <v>-0.02869341648514914</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.01621929215982487</v>
+        <v>-0.05974793029525573</v>
       </c>
       <c r="BR3" t="n">
         <v>-0</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.1893382395793216</v>
+        <v>-0.2874788695115575</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
         <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.09683807727074757</v>
+        <v>-0.01658852782864263</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.1554974355091424</v>
+        <v>0.179660316488808</v>
       </c>
       <c r="CA3" t="n">
         <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1787705779995226</v>
+        <v>0.2187557382420026</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0717589406160572</v>
+        <v>-0.003651142734741556</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.2090931499327498</v>
+        <v>-0.0876990563940815</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
         <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
         <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.2190874922434067</v>
+        <v>0.2039653908842954</v>
       </c>
       <c r="CO3" t="n">
         <v>0</v>
@@ -1850,40 +1850,40 @@
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.05483143591776855</v>
+        <v>-0.05221228247092363</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1680295747936069</v>
+        <v>-0.1177518144325417</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT3" t="n">
         <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.1768157856202969</v>
+        <v>0.2197112133078801</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.1077057193695699</v>
+        <v>-0.005293870051670879</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0.1848690855658262</v>
+        <v>-0.098781988045811</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1895,76 +1895,76 @@
         <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.2095158532770484</v>
+        <v>0.1329120330013933</v>
       </c>
       <c r="DG3" t="n">
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.4638147544562953</v>
+        <v>0.125789356054729</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.03067144500972382</v>
+        <v>-0.03281987720679097</v>
       </c>
       <c r="DK3" t="n">
         <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.07177072221924095</v>
+        <v>0.119180493240094</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ3" t="n">
         <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.04785098993027817</v>
+        <v>-0.03206127729927718</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.05362524308339568</v>
+        <v>-0.1495012537306301</v>
       </c>
       <c r="DT3" t="n">
         <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.1198949593127527</v>
+        <v>0.1616594029033398</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.01534603344344278</v>
+        <v>-0.07631190129339353</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.05196255109410167</v>
+        <v>-0.0870008575037958</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
         <v>-0</v>
@@ -1973,25 +1973,25 @@
         <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.1770581478522699</v>
+        <v>0.1440787426176997</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.1144598983373158</v>
+        <v>0.01779200751899038</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.239031830952025</v>
+        <v>0.05269704336457835</v>
       </c>
       <c r="EL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
@@ -2000,10 +2000,10 @@
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.2411851586072027</v>
+        <v>0.08451548401514047</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
@@ -2012,10 +2012,10 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.0203422858348315</v>
+        <v>0.04121342011220695</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.06274981730326434</v>
+        <v>0.005385765292973205</v>
       </c>
       <c r="EU3" t="n">
         <v>-0</v>
@@ -2024,67 +2024,67 @@
         <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.1778856600445262</v>
+        <v>0.2178520716643917</v>
       </c>
       <c r="EZ3" t="n">
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.08297070209127283</v>
+        <v>0.02484120574946469</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0.1612714950076537</v>
+        <v>-0.07926650996248383</v>
       </c>
       <c r="FD3" t="n">
         <v>-0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.0282257471536892</v>
+        <v>-0.1209459398113599</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.1075289515602455</v>
+        <v>-0.08657637926967719</v>
       </c>
       <c r="FL3" t="n">
-        <v>-0.1402432879478821</v>
+        <v>-0.09008053888134408</v>
       </c>
       <c r="FM3" t="n">
         <v>-0</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.1064274147369041</v>
+        <v>0.3368381922428222</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,46 +2093,46 @@
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.2456477986219479</v>
+        <v>0.07339216822064522</v>
       </c>
       <c r="FU3" t="n">
-        <v>-0.09086484745557065</v>
+        <v>-0.04299618811281111</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.05948860629039076</v>
+        <v>0.2109866685672859</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
         <v>0</v>
       </c>
       <c r="GC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.07853740624476381</v>
+        <v>-0.1045783343740819</v>
       </c>
       <c r="GE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF3" t="n">
         <v>-0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2140,7 +2140,7 @@
         <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3874508007704472</v>
+        <v>0.3689742744816598</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,10 +2149,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03395047077138494</v>
+        <v>0.1650506542453078</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2270755947483766</v>
+        <v>-0.3911077004248557</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
@@ -2161,25 +2161,25 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2078949993413584</v>
+        <v>0.2865812871864603</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01665115902997345</v>
+        <v>-0.00308863691702063</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.08399396893410399</v>
+        <v>-0.1601326452850972</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05124363046503104</v>
+        <v>0.1889746448892282</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,40 +2203,40 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.03474747844822836</v>
+        <v>-0.06332925105268207</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.02848589941331603</v>
+        <v>-0.05097736735444575</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.08163047361287627</v>
+        <v>-0.06310244345386218</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.06390554835520706</v>
+        <v>-0.1734091675740372</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0601360128454887</v>
+        <v>-0.06238500738122154</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03528432908802498</v>
+        <v>0.1140678119274498</v>
       </c>
       <c r="AM4" t="n">
         <v>-0</v>
@@ -2257,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.02465296591839248</v>
+        <v>0.05259346650823601</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.0907374007027431</v>
+        <v>-0.1126968880214315</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>-0</v>
@@ -2272,22 +2272,22 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3636428938291119</v>
+        <v>0.758304901151171</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.06890869245370645</v>
+        <v>-0.1213932481118595</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.29304359016392</v>
+        <v>-0.4418352527304096</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2296,13 +2296,13 @@
         <v>-0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.07672306905817323</v>
+        <v>-0.1116489434615641</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,67 +2311,67 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.07070100971356208</v>
+        <v>-0.07697921769477808</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.06553800182200217</v>
+        <v>-0.1267449310943204</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.08637630851226828</v>
+        <v>0.002663293906827971</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.001475737793474285</v>
+        <v>0.06816695132611643</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01741295459082627</v>
+        <v>0.07239039774720758</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.199602765201402</v>
+        <v>0.4441413032544888</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.01897883554475324</v>
+        <v>0.04084042963542128</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.06930112512133839</v>
+        <v>-0.2003757766476837</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>-0</v>
@@ -2383,22 +2383,22 @@
         <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.1113829091331204</v>
+        <v>-0.1719237943028544</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.01671776322695669</v>
+        <v>-0.08232232339133323</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.06135427436978785</v>
+        <v>0.2095910375843398</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
@@ -2410,19 +2410,19 @@
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.05186765005826738</v>
+        <v>-0.1531262598871556</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.04068156694082709</v>
+        <v>0.1911935575586263</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.08302641975684767</v>
+        <v>0.2200657473275799</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2437,22 +2437,22 @@
         <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.08589147513533725</v>
+        <v>-0.1723561622026057</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.02320226993904255</v>
+        <v>-0.07455561645967325</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.07034243246373514</v>
+        <v>0.2311320413290852</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
         <v>-0</v>
@@ -2464,19 +2464,19 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.01714624372519016</v>
+        <v>0.01783943030857484</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.03175762329123736</v>
+        <v>-0.01779373519726786</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.09261563172504649</v>
+        <v>0.1184607397674248</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,28 +2485,28 @@
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.04455139915004754</v>
+        <v>-0.08345327930815402</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.0135758851142028</v>
+        <v>0.003991348530744019</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.04760532894810022</v>
+        <v>0.1789446927626772</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2515,55 +2515,55 @@
         <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.08812736933929809</v>
+        <v>-0.06240988088444378</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.02864528670791508</v>
+        <v>-0.08204098866269528</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.008886485838232226</v>
+        <v>0.1582719530537609</v>
       </c>
       <c r="EC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED4" t="n">
         <v>-0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.07907337974505371</v>
+        <v>-0.08842807551226446</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI4" t="n">
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.02945328416302426</v>
+        <v>-0.142257033881479</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.00332572680377346</v>
+        <v>0.03393796481575272</v>
       </c>
       <c r="EL4" t="n">
         <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
@@ -2572,25 +2572,25 @@
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.03333430082441175</v>
+        <v>0.1000589998565423</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
         <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.005722260726156698</v>
+        <v>0.175425133827316</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.01162771201323424</v>
+        <v>-0.009875619799558893</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
         <v>-0</v>
@@ -2599,46 +2599,46 @@
         <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.08376080747467379</v>
+        <v>-0.1837592942890948</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.02378717644474544</v>
+        <v>-0.1264787602761766</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.06674066193412108</v>
+        <v>0.2131782143112758</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01036202341403117</v>
+        <v>-0.1275924665298852</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.05623563800697546</v>
+        <v>0.07303199071803024</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0.09894140802520782</v>
+        <v>-0.222385837270284</v>
       </c>
       <c r="FM4" t="n">
         <v>-0</v>
@@ -2653,7 +2653,7 @@
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.08322598738839902</v>
+        <v>-0.2099911099334049</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
@@ -2662,10 +2662,10 @@
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.04570183379035343</v>
+        <v>-0.1980996301738367</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0.03495818265062459</v>
+        <v>-0.04811832464166422</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2677,28 +2677,28 @@
         <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02367351295933759</v>
+        <v>-0.0249324206361851</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.08824629353410182</v>
+        <v>0.1050056991679351</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG4" t="n">
         <v>-0</v>
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.06224943633368885</v>
+        <v>0.4025068550582929</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,25 +3287,25 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0114209267401579</v>
+        <v>-0.01303262204064907</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.02740243685190335</v>
+        <v>-0.1814475672826049</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01671256548445396</v>
+        <v>0.3901036331655288</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,79 +3314,79 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01502450176646141</v>
+        <v>-0.1076451944938191</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001184291032769072</v>
+        <v>-0.007180889633451467</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.001556396622077524</v>
+        <v>0.147701349900364</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0109133616553189</v>
+        <v>-0.04564369830769243</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01836830858538081</v>
+        <v>0.04659004755523934</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02035296746675229</v>
+        <v>-0.01549967698131931</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02225610772645462</v>
+        <v>-0.2424634602466643</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.009062274825080737</v>
+        <v>0.04135043636656003</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.01252364605983017</v>
+        <v>0.1214964253099581</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,16 +3395,16 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.00504138848206248</v>
+        <v>0.006395858371986256</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.006518174836278194</v>
+        <v>-0.08021806993467245</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.06901274306167544</v>
+        <v>0.5652777375698954</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3422,10 +3422,10 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.01334082641118218</v>
+        <v>-0.2688979729518705</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.01492540330220632</v>
+        <v>-0.240478883155907</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3434,40 +3434,40 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.01777082046096212</v>
+        <v>-0.01801510372379138</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.009727269197194613</v>
+        <v>-0.0845265062478139</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.004726103043218043</v>
+        <v>-0.03452081430655007</v>
       </c>
       <c r="BI6" t="n">
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.03490764249113346</v>
+        <v>0.03828414556532017</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
@@ -3476,13 +3476,13 @@
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01983525758967593</v>
+        <v>0.1244255732804754</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01235869720408697</v>
+        <v>0.07878427064913843</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>0</v>
@@ -3491,25 +3491,25 @@
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.02703597504151779</v>
+        <v>0.3840121243773281</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.02403148486275934</v>
+        <v>-0.03036570244699117</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01858641686547517</v>
+        <v>-0.08674990724606475</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>-0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.002234446736254342</v>
+        <v>-0.1567066807345086</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.002360752079200103</v>
+        <v>0.02174884498902516</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.01518875879815906</v>
+        <v>0.10423122031365</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3545,52 +3545,52 @@
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0092330499435115</v>
+        <v>-0.2120357973813613</v>
       </c>
       <c r="CO6" t="n">
         <v>0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.005933552745769359</v>
+        <v>0.2793628904413246</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.03118092089990477</v>
+        <v>0.0331040107053388</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0004665478950981532</v>
+        <v>-0.1436626893469485</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.002164285582403092</v>
+        <v>0.01703849515883938</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.01801410187019785</v>
+        <v>0.1148085031799085</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
@@ -3602,49 +3602,49 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0001361144816858302</v>
+        <v>-0.109378348379075</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.01749953784304399</v>
+        <v>-0.09415066028471029</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01387908731390689</v>
+        <v>0.1119493910704656</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.00100578117325801</v>
+        <v>-0.1143770189591608</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01729127750131859</v>
+        <v>-0.03394021361867407</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.005484286883990138</v>
+        <v>0.02071078152718207</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
         <v>-0</v>
@@ -3656,103 +3656,103 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.02190529090153009</v>
+        <v>0.01442970464216181</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
         <v>0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.03121019965008268</v>
+        <v>-0.07980203819597292</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.01495338696032404</v>
+        <v>0.05733001046038776</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>4.40058778072375e-05</v>
+        <v>-0.02621432081799353</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.002716373875677202</v>
+        <v>-0.04318044673417041</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.006223908973884969</v>
+        <v>0.02728881097501138</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.008985119500760025</v>
+        <v>-0.07292036958535307</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.02272589096221852</v>
+        <v>-0.1818891993112179</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.03944972242948464</v>
+        <v>-0.1511008054538928</v>
       </c>
       <c r="EU6" t="n">
         <v>-0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.004265206278172327</v>
+        <v>-0.1729244454958219</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.003206415078600628</v>
+        <v>0.001693657894229192</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.01967251591599786</v>
+        <v>0.09075857087260235</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
@@ -3764,34 +3764,34 @@
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.02127645294242974</v>
+        <v>-0.1462999847568822</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.03155241481391572</v>
+        <v>0.155699452440295</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.00601853008126948</v>
+        <v>0.08787541428279669</v>
       </c>
       <c r="FM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.005764667468911485</v>
+        <v>0.02581045727743503</v>
       </c>
       <c r="FR6" t="n">
         <v>0</v>
@@ -3800,25 +3800,25 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.008476663023248385</v>
+        <v>-0.05954963291408526</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.03280955647058911</v>
+        <v>-0.08207360450573091</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.01225664623687978</v>
+        <v>-0.06625404748057324</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
@@ -3830,13 +3830,13 @@
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.006697259039169762</v>
+        <v>0.03294836149071864</v>
       </c>
       <c r="GE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2652664475030307</v>
+        <v>0.4163796439156767</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.09325340356073333</v>
+        <v>-0.2040002778799453</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06988725101901165</v>
+        <v>-0.04473187228513793</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,25 +3868,25 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1605030235446298</v>
+        <v>0.3752560386547648</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.04710822884591285</v>
+        <v>-0.1224565576376072</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.08514537463084741</v>
+        <v>-0.07639689405215749</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7" t="n">
         <v>-0</v>
@@ -3898,73 +3898,73 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06431317181450134</v>
+        <v>0.09693978725821456</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01635446035742453</v>
+        <v>-0.06767818708622028</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03294969041300178</v>
+        <v>-0.1103261831697296</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.07944423913867073</v>
+        <v>-0.1124112665788822</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.0397042123027938</v>
+        <v>-0.07582709557273878</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0008109963619231852</v>
+        <v>-0.1017630366015979</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01742706391422246</v>
+        <v>0.124771814108236</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.02631346826749787</v>
+        <v>-0.09778126686047037</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.05340751852325941</v>
+        <v>0.04723460025279644</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3973,34 +3973,34 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.3298064580889729</v>
+        <v>0.394740332085769</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.006624944764529754</v>
+        <v>-0.19879789019748</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1140736179420841</v>
+        <v>-0.2721656133019321</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
@@ -4009,16 +4009,16 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02030331822467515</v>
+        <v>-0.04351158936855416</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.03384676526644614</v>
+        <v>-0.02148763348931552</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1036884694588265</v>
+        <v>-0.01484098588222163</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.07850916575384327</v>
+        <v>-0.02016797120469295</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.06521045282843832</v>
+        <v>0.06221387516072648</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.08048964616927427</v>
+        <v>0.02036710770300797</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,49 +4063,49 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1485442861897867</v>
+        <v>0.3225978055702576</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.002508761288223753</v>
+        <v>-0.1748629511136814</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.03051742144025043</v>
+        <v>-0.1074711416331629</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.05752507748863129</v>
+        <v>-0.1493336633443407</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.006065318679843465</v>
+        <v>0.1669857318271202</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0004252281769985802</v>
+        <v>0.009437431033570358</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4117,22 +4117,22 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.04339387129406846</v>
+        <v>-0.09130581854775076</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.08630849986522827</v>
+        <v>0.256480098537918</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.0832420540637121</v>
+        <v>0.1272656886519231</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT7" t="n">
         <v>-0</v>
@@ -4144,25 +4144,25 @@
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.03931765052321663</v>
+        <v>-0.142975193384505</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.02371364483347937</v>
+        <v>0.1851649094994135</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.001915230437197968</v>
+        <v>0.01591783369274805</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
@@ -4171,22 +4171,22 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.0004375120734241249</v>
+        <v>-0.1488205646202565</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.01615065637976668</v>
+        <v>0.08193475906580658</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.01487349237295285</v>
+        <v>-0.08732204800227261</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
@@ -4198,103 +4198,103 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.05139983726536106</v>
+        <v>-0.07549954706557929</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.05461472931191981</v>
+        <v>0.09023596693852917</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.004989343966424962</v>
+        <v>-0.009624929771615479</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.03538655913676677</v>
+        <v>0.03914735078133072</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.03182348403502251</v>
+        <v>0.02857826458407612</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01354774312725723</v>
+        <v>0.01219951936165447</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
         <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.02713376799883064</v>
+        <v>-0.08987752719156988</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.07590011708084718</v>
+        <v>0.1238023846981341</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.03578956315362165</v>
+        <v>0.0298953164394387</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.04834918944509249</v>
+        <v>-0.08095078771802035</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.04144476314900959</v>
+        <v>-0.1297197590463707</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.01040967670143023</v>
+        <v>-0.03050445592059803</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4303,76 +4303,76 @@
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.04802192912613931</v>
+        <v>-0.1597215199419307</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.01856460359664011</v>
+        <v>0.1912521311153617</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01173117629432144</v>
+        <v>0.0009540625720578916</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.0405729457343973</v>
+        <v>-0.1084449721289497</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.04545136167327622</v>
+        <v>0.1239480420543421</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02195954387739732</v>
+        <v>-0.01135986486207753</v>
       </c>
       <c r="FL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.001390178938890903</v>
+        <v>0.009281119063868522</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.01088834345498924</v>
+        <v>0.1615269195816717</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.04189746052114594</v>
+        <v>-0.02933274889275689</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4384,31 +4384,31 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.006303847694071393</v>
+        <v>-0.1102586117589336</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.01927570199074076</v>
+        <v>0.0935806602639412</v>
       </c>
       <c r="GC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4982,46 +4982,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2813035719948727</v>
+        <v>0.1342757826556876</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0301008823231791</v>
+        <v>-0.03967484667465901</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.05643782752801008</v>
+        <v>-0.047255566457566</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1449406442154503</v>
+        <v>0.1247052862313151</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.01227820440265649</v>
+        <v>-0.02077065313783184</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.05214580352960676</v>
+        <v>-0.06004793771139563</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5033,76 +5033,76 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.04178432427669106</v>
+        <v>0.03403250115685673</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.02043399758191116</v>
+        <v>-0.006826116560858176</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03999173490385394</v>
+        <v>-0.005565845234103491</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.04844257036043886</v>
+        <v>-0.01685763111074716</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.01199536932348555</v>
+        <v>-0.05774241751346948</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.005327766004050346</v>
+        <v>-0.07817665841013803</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.0148863883364908</v>
+        <v>0.04135626026960884</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.01167318656378591</v>
+        <v>-0.004370168415885798</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.03011800953279444</v>
+        <v>0.03905529185903549</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5120,43 +5120,43 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.2594349257693344</v>
+        <v>0.1564423869773919</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.03112393365565282</v>
+        <v>-0.007111845929371458</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.05296356718650179</v>
+        <v>-0.09542267543937714</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.05950022986860797</v>
+        <v>-0.03917339689565478</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.05342703258022106</v>
+        <v>-0.009873997987743516</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.04975569349601068</v>
+        <v>-0.01204930834999856</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,19 +5174,19 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.106985337916301</v>
+        <v>0.03026435844479891</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01641749343003522</v>
+        <v>0.01947728916840046</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.09260111423073636</v>
+        <v>0.05611009239326008</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
         <v>0</v>
@@ -5201,76 +5201,76 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1307778550860325</v>
+        <v>0.1288817978251809</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.02320385709261587</v>
+        <v>-0.03820017863880809</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.02381837787731442</v>
+        <v>-0.01578196340958453</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.05267134566128882</v>
+        <v>-0.04168137027207088</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0.005832734112573052</v>
+        <v>0.03919552041920702</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.005641751575165319</v>
+        <v>0.02174822804017522</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.05886561677130826</v>
+        <v>-0.05535210717660182</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.03483614577236063</v>
+        <v>0.03993730303716059</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.06252193968245229</v>
+        <v>0.0335159015240873</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
         <v>-0</v>
@@ -5279,19 +5279,19 @@
         <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.03537030496982597</v>
+        <v>-0.03912525828454212</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.006124552125493847</v>
+        <v>0.0433263957802615</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.002955863352439839</v>
+        <v>0.02547000584407275</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
@@ -5300,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,73 +5309,73 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.009049605335281114</v>
+        <v>-0.0003258051571426022</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.05063832496443729</v>
+        <v>0.00914580504964534</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.007324616173862491</v>
+        <v>-0.006124351925796613</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.062938030785407</v>
+        <v>-0.03991083570208818</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.003870150912557851</v>
+        <v>-0.0213779788329482</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01715135228154514</v>
+        <v>-0.01531760991979086</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.001620471671114557</v>
+        <v>0.04238425775678643</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.00997841698006505</v>
+        <v>0.01972644230663211</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.03203509119809108</v>
+        <v>-0.06118491985756788</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
@@ -5384,22 +5384,22 @@
         <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.03387613475128066</v>
+        <v>0.007891056157782831</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0.001585720219689498</v>
+        <v>0.02893097962195065</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.04901037069550478</v>
+        <v>0.04513457475773532</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
@@ -5408,7 +5408,7 @@
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
@@ -5417,19 +5417,19 @@
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.02368006165593776</v>
+        <v>-0.03210221107597389</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.006879093251294921</v>
+        <v>0.0447269295332429</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.02384752590249433</v>
+        <v>-0.008190651925803798</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
         <v>0</v>
@@ -5438,22 +5438,22 @@
         <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.03412589096124122</v>
+        <v>-0.04708678232759928</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0001089485766206362</v>
+        <v>0.05015285510703023</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.01320349637276338</v>
+        <v>0.01439121254656846</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
@@ -5462,25 +5462,25 @@
         <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0149542454249308</v>
+        <v>-0.002102311632746347</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.01884184398715685</v>
+        <v>0.003952372824172428</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.0357610994547067</v>
+        <v>-0.02527212268180276</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
@@ -5489,31 +5489,31 @@
         <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.02803855844894806</v>
+        <v>0.01691956722382474</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.01376656434050059</v>
+        <v>0.05083773509656869</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.007241233376714142</v>
+        <v>-0.05069353223879568</v>
       </c>
       <c r="FU9" t="n">
         <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
@@ -5525,28 +5525,28 @@
         <v>-0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.004899291516374995</v>
+        <v>-0.01836987922747576</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.0186763988837574</v>
+        <v>0.007330420139009674</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
         <v>0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,19 +5554,19 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1753325542458682</v>
+        <v>0.174478842369749</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.001861025648660907</v>
+        <v>-0.04144901042085377</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1201682660389519</v>
+        <v>-0.1267912077971837</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -5578,37 +5578,37 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1168889493713425</v>
+        <v>0.3303171761512816</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.01017045448786457</v>
+        <v>-0.09647810591724895</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.08542626605887788</v>
+        <v>-0.1175868999652359</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.008446767148017184</v>
+        <v>0.07503975655227844</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
@@ -5617,37 +5617,37 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01278187809399203</v>
+        <v>-0.07235077454018778</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.002970754225196949</v>
+        <v>-0.005628909027437738</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.02394926874866394</v>
+        <v>-0.02683181032311454</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01781980329618022</v>
+        <v>-0.2093013860391321</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.009280291295394521</v>
+        <v>-0.03949539815828559</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
@@ -5656,28 +5656,28 @@
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.003413801094535957</v>
+        <v>0.02698788062332071</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.01244339580283066</v>
+        <v>-0.009244415801575702</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.02616287028459998</v>
+        <v>-0.02344256326774017</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5686,37 +5686,37 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1234868949431828</v>
+        <v>0.4109888796755349</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.005904159878943866</v>
+        <v>-0.1266299632621384</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.0617998178080619</v>
+        <v>-0.1030469045969443</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0579982268392056</v>
+        <v>-0.07936886362355035</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,25 +5725,25 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.02605781511664183</v>
+        <v>-0.08773568225441893</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.04952963543871915</v>
+        <v>-0.0389523222560061</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.05518064957611164</v>
+        <v>0.1330436717393748</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
@@ -5752,16 +5752,16 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.03374109603009773</v>
+        <v>0.07342477472382317</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.006923230405654165</v>
+        <v>-0.00379958294834209</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT10" t="n">
         <v>0</v>
@@ -5770,19 +5770,19 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.05694431402149773</v>
+        <v>0.2678748415944099</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.00878505706844354</v>
+        <v>-0.05172951163299713</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.0137865728751884</v>
+        <v>-0.04168373657739333</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
@@ -5791,67 +5791,67 @@
         <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.03215815943760334</v>
+        <v>-0.05958964371256111</v>
       </c>
       <c r="CF10" t="n">
         <v>0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.004434494349291136</v>
+        <v>0.04117746511200641</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.02646885193407263</v>
+        <v>0.05472550722600986</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.02154523065644725</v>
+        <v>-0.2274591676325248</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.01984179989931486</v>
+        <v>0.1428753107660158</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.01176309421974564</v>
+        <v>0.07267639868828193</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
         <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.02096775553385949</v>
+        <v>-0.05038574432753376</v>
       </c>
       <c r="CX10" t="n">
         <v>-0</v>
@@ -5860,10 +5860,10 @@
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.004598259934741873</v>
+        <v>0.01925330834448611</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.02479488552370201</v>
+        <v>0.05940478310713408</v>
       </c>
       <c r="DB10" t="n">
         <v>0</v>
@@ -5875,25 +5875,25 @@
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.00942792377255054</v>
+        <v>0.01433729055358203</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.001745953236460921</v>
+        <v>-0.0293997212346517</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.003802847433232294</v>
+        <v>-0.001367782431143341</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
         <v>-0</v>
@@ -5902,118 +5902,118 @@
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.02257252574968996</v>
+        <v>-0.08859332234811762</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01153485178943712</v>
+        <v>0.06423165069586634</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.006552027293018942</v>
+        <v>0.000375969394743544</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
         <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.001428693419632627</v>
+        <v>0.04005598453323687</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.0113888537677719</v>
+        <v>-0.01422987406327267</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.006446938993383253</v>
+        <v>-0.05936552018947529</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.01541279637381846</v>
+        <v>0.04916102945361696</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
         <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.006183279215854137</v>
+        <v>-0.007815370506523516</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.016938949630433</v>
+        <v>0.02698671359498315</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
         <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.01768352447244188</v>
+        <v>0.009683560396128377</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0005301889719515236</v>
+        <v>-0.03912535894147016</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.03615955052527879</v>
+        <v>0.05214851045317084</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.0236515397506165</v>
+        <v>-0.06739984964739432</v>
       </c>
       <c r="EZ10" t="n">
         <v>0</v>
@@ -6022,79 +6022,79 @@
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.001030799584953018</v>
+        <v>0.0150785992854734</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.02870306760235427</v>
+        <v>0.0552844047321437</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.002023748522333679</v>
+        <v>-0.05227630282541201</v>
       </c>
       <c r="FI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ10" t="n">
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.02117964532220485</v>
+        <v>0.03101400592166563</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.01691733208547199</v>
+        <v>0.03434694006940268</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
         <v>0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.0102355319626828</v>
+        <v>-0.01781511471390874</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.0214387972297884</v>
+        <v>-0.07785909888902053</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.001205723560567617</v>
+        <v>0.00452072824780483</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
         <v>-0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.02293660569364711</v>
+        <v>0.00969624501062041</v>
       </c>
       <c r="GA10" t="n">
         <v>-0</v>
@@ -6106,13 +6106,13 @@
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.0188488363080928</v>
+        <v>-0.02212723997940815</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG10" t="n">
         <v>0</v>
@@ -6120,28 +6120,28 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3345422045462771</v>
+        <v>0.2046570568045433</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1040163273759496</v>
+        <v>-0.1391635265088232</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.05689265839859305</v>
+        <v>0.1642240210055048</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6153,22 +6153,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2614667340631677</v>
+        <v>0.1989677382213334</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1237982883111269</v>
+        <v>-0.1527060369184444</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1247101020966574</v>
+        <v>0.09332410777899654</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -6180,19 +6180,19 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09688481565730274</v>
+        <v>0.03678761588890494</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.02582500224957221</v>
+        <v>-0.04709897140511093</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03479458580762092</v>
+        <v>-0.04232896098443257</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>-0</v>
@@ -6204,79 +6204,79 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.06004206032099968</v>
+        <v>0.04169451288128199</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.03800396211726926</v>
+        <v>0.1198136114214554</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.03052996765202319</v>
+        <v>0.0438756101125208</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.01928273281468286</v>
+        <v>0.04289646507611577</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.03078338412302969</v>
+        <v>-0.05927434488464093</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.06248062317465185</v>
+        <v>0.0002574403764750146</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.1529712139775669</v>
+        <v>0.1815730724655879</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.01858769403671884</v>
+        <v>-0.2317369779039581</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.1708608151468087</v>
+        <v>-0.01095831038251931</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
         <v>-0</v>
@@ -6285,16 +6285,16 @@
         <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.0923004019583504</v>
+        <v>-0.001130502493756582</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.03984387068528213</v>
+        <v>0.1227698334268079</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.08900320377887121</v>
+        <v>0.07453582658333616</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6309,49 +6309,49 @@
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.03816941572154151</v>
+        <v>-0.06788467592370474</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.05536851891374819</v>
+        <v>-0.07743821907492983</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.1198218264601084</v>
+        <v>-0.1309883022584341</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.05954179341908349</v>
+        <v>0.1040804621528268</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0.02141594148381698</v>
+        <v>-0.1085156542285857</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.1117756655233817</v>
+        <v>-0.01275830279656665</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
         <v>0</v>
@@ -6360,28 +6360,28 @@
         <v>-0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF11" t="n">
-        <v>-0.06959294209998884</v>
+        <v>-0.07832564682673127</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.02686093877623242</v>
+        <v>0.07135817575842671</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0004054989506993912</v>
+        <v>-0.04327651232711442</v>
       </c>
       <c r="CI11" t="n">
         <v>0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6390,19 +6390,19 @@
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.01418004503149746</v>
+        <v>-0.007151148316827923</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.003704657935527651</v>
+        <v>0.1652076682098198</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.1186674801633818</v>
+        <v>0.007519312428672886</v>
       </c>
       <c r="CR11" t="n">
         <v>0</v>
@@ -6411,34 +6411,34 @@
         <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
         <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0.05369284244981106</v>
+        <v>-0.05779338323976645</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.02648432469705512</v>
+        <v>0.06721353446840408</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.02319440181703224</v>
+        <v>-0.05769385527764437</v>
       </c>
       <c r="DA11" t="n">
         <v>-0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,16 +6447,16 @@
         <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG11" t="n">
-        <v>-0.03659946683637923</v>
+        <v>-0.01125307929713036</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.04330106983779596</v>
+        <v>0.02006291002408327</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0.0056095734747765</v>
+        <v>-0.01911323884671937</v>
       </c>
       <c r="DJ11" t="n">
         <v>0</v>
@@ -6468,31 +6468,31 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
         <v>-0</v>
       </c>
       <c r="DP11" t="n">
-        <v>-0.001868307312742693</v>
+        <v>-0.01811503225790511</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.02712015548731022</v>
+        <v>0.06966897874401506</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.1420395710614809</v>
+        <v>-0.06457514737998893</v>
       </c>
       <c r="DS11" t="n">
         <v>-0</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
@@ -6501,16 +6501,16 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.06473487613125521</v>
+        <v>0.02306792157768963</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.002457176101492261</v>
+        <v>0.002836824704821441</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.05875099378788502</v>
+        <v>0.07843873381304853</v>
       </c>
       <c r="EB11" t="n">
         <v>0</v>
@@ -6525,46 +6525,46 @@
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0.1110914001496662</v>
+        <v>-0.04259690716461582</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.04635818549333129</v>
+        <v>0.01440926960917821</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.05896696643402607</v>
+        <v>0.01298690560050956</v>
       </c>
       <c r="EK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
         <v>0</v>
       </c>
       <c r="EQ11" t="n">
-        <v>-0.006860286306501331</v>
+        <v>-0.04952080273176031</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.030564743052281</v>
+        <v>0.07976747118282944</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.02856841084114657</v>
+        <v>0.03088273895205181</v>
       </c>
       <c r="ET11" t="n">
         <v>0</v>
@@ -6573,79 +6573,79 @@
         <v>0</v>
       </c>
       <c r="EV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ11" t="n">
-        <v>-0.06724749697577918</v>
+        <v>-0.06279178689186302</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.04259430827403628</v>
+        <v>0.1039865954783983</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.02112461941074566</v>
+        <v>-0.04352554438357284</v>
       </c>
       <c r="FC11" t="n">
         <v>0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0.004725861477240727</v>
+        <v>-0.01953607261565314</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.005285212820973009</v>
+        <v>0.05611485805274248</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.07268587174485637</v>
+        <v>-0.03833534244464248</v>
       </c>
       <c r="FL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0.004240599187395422</v>
+        <v>-0.0002425550803640829</v>
       </c>
       <c r="FS11" t="n">
-        <v>-0.007104763743604158</v>
+        <v>-0.009901281984594551</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.09031323925689508</v>
+        <v>0.2642630620146642</v>
       </c>
       <c r="FU11" t="n">
         <v>0</v>
@@ -6654,22 +6654,22 @@
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.04626409388790098</v>
+        <v>-0.02756181751235361</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0.05480273634979909</v>
+        <v>0.147349977541285</v>
       </c>
       <c r="GC11" t="n">
         <v>-0</v>
@@ -6692,19 +6692,19 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.185761519164108</v>
+        <v>0.2373337824054026</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08280529374313922</v>
+        <v>-0.04664687109060651</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.05906482528137331</v>
+        <v>-0.1340200125569248</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
@@ -6719,34 +6719,34 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1296497095568202</v>
+        <v>0.3315054476781985</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05609002565123491</v>
+        <v>-0.1098442723696418</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.03579135002131095</v>
+        <v>-0.08628771016387786</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01864672818254303</v>
+        <v>0.04872839620026031</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
@@ -6755,40 +6755,40 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.02887223281028661</v>
+        <v>-0.03340991195670458</v>
       </c>
       <c r="X12" t="n">
-        <v>0.02786397998979286</v>
+        <v>0.008096385628725463</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0305368007271461</v>
+        <v>-0.01956221671455853</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.02202576027203309</v>
+        <v>-0.1385505748666266</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.003733405023159691</v>
+        <v>0.01043333309798664</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6797,25 +6797,25 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.02968125502208196</v>
+        <v>0.04047913756227129</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.01786262120572332</v>
+        <v>-0.03809372585761372</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.02616291587461859</v>
+        <v>-0.02875975100417511</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6824,118 +6824,118 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1149478478685116</v>
+        <v>0.2745906257057886</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.0609388444850836</v>
+        <v>-0.1416871081255964</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.04359743020474337</v>
+        <v>-0.1303191517975555</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.04113471601615659</v>
+        <v>0.008643997258531584</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.033586889642026</v>
+        <v>-0.06500036801438434</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.008106854990944429</v>
+        <v>-0.02634758994888761</v>
       </c>
       <c r="BI12" t="n">
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.05040382219578231</v>
+        <v>0.05444417493742189</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.02459522723025488</v>
+        <v>0.06717108733144284</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.01557470893925633</v>
+        <v>0.03110582372546847</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.06765178711632917</v>
+        <v>0.162188570237383</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.03238911692027842</v>
+        <v>-0.04971851313415511</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.01062193215397759</v>
+        <v>-0.04817218318348154</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD12" t="n">
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.02639414156272516</v>
+        <v>-0.06009311427689332</v>
       </c>
       <c r="CF12" t="n">
         <v>0</v>
@@ -6944,10 +6944,10 @@
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.008559142952868666</v>
+        <v>0.04657745749659409</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.01613051095244695</v>
+        <v>0.0473388649676917</v>
       </c>
       <c r="CJ12" t="n">
         <v>-0</v>
@@ -6956,25 +6956,25 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.001681295693012171</v>
+        <v>-0.1402564251143357</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
         <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.01275195504509536</v>
+        <v>0.1663840163365967</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.02093154650694527</v>
+        <v>0.02888167853639684</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6983,25 +6983,25 @@
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.01952888184489697</v>
+        <v>-0.05969681219856627</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.004553180121479291</v>
+        <v>0.02477936644056983</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.02295379872539117</v>
+        <v>0.05340759886381242</v>
       </c>
       <c r="DB12" t="n">
         <v>0</v>
@@ -7016,76 +7016,76 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.009446839789090784</v>
+        <v>-0.02083197696270756</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.008389746392797848</v>
+        <v>-0.009575962464975501</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0.004198287361923691</v>
+        <v>0.01331555364932408</v>
       </c>
       <c r="DK12" t="n">
         <v>0</v>
       </c>
       <c r="DL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.02386988757301259</v>
+        <v>-0.04542119480032425</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.02125622512683335</v>
+        <v>0.02420069833244502</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.02144786251296666</v>
+        <v>0.05889706618060261</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.005336672732941069</v>
+        <v>0.009052221199594909</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.02320332016238783</v>
+        <v>-0.03972497463145754</v>
       </c>
       <c r="EB12" t="n">
-        <v>-0.01488335116879579</v>
+        <v>0.02351453101027287</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
@@ -7094,64 +7094,64 @@
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.01621237883264771</v>
+        <v>-0.01691858519304042</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.01577216402764448</v>
+        <v>-0.01511575908304665</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.007292625230345929</v>
+        <v>0.04132552207182115</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.0006805769808963989</v>
+        <v>-0.01247909489221269</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.0091960118702764</v>
+        <v>-0.0351153914092676</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0.02677545493915625</v>
+        <v>-0.04888710252002696</v>
       </c>
       <c r="EU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.01688998410672381</v>
+        <v>-0.06777234964664682</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
@@ -7160,13 +7160,13 @@
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.001741843322154773</v>
+        <v>0.02912177892940906</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0234164705170184</v>
+        <v>0.04570943807231771</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
@@ -7178,7 +7178,7 @@
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.02039740211811467</v>
+        <v>-0.05752168489926519</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
@@ -7187,25 +7187,25 @@
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.03842939906323027</v>
+        <v>0.05886615091126102</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.01951696093881562</v>
+        <v>-0.02431818055466254</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.002203766585031614</v>
+        <v>-0.004117442018878573</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,43 +7214,43 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.001105556594987681</v>
+        <v>0.003514809466212202</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.01600898399904726</v>
+        <v>-0.01279937676912598</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.02248658517898526</v>
+        <v>-0.0420893872409336</v>
       </c>
       <c r="GA12" t="n">
         <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.02490499780259479</v>
+        <v>0.02395882063395312</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>0</v>
